--- a/public/master_tracker.xlsx
+++ b/public/master_tracker.xlsx
@@ -494,6 +494,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -525,10 +526,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Last refreshed: 2026-04-25</t>
-        </is>
-      </c>
-    </row>
+          <t>Last refreshed: 2026-09-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
@@ -592,6 +594,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
@@ -6184,31 +6187,46 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>AI-assisted</t>
+          <t>Human-reviewed</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>https://www.moroccoworldnews.com/2026/01/274765/morocco-launches-maroc-ia-2030-roadmap-to-strengthen-ai-governance-digital-sovereignty/</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>National AI Strategy in development under ADD; not formally launched</t>
+          <t>[Corrected 2026-09-17] Strategy 'Maroc IA 2030' formally launched 2026-01-12 by the Ministry of Digital Transition, with the JAZARI ROOT institute created same day. Was: 'in development, not formally launched.'</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>AI-assisted (Cowork v2026-04-25)</t>
+          <t>AI sweep 2026-09-16 + author-approved correction</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Akwasi Appiah Obeng</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
@@ -6424,31 +6442,46 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>AI-assisted</t>
+          <t>Human-reviewed</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>https://techafricanews.com/2026/01/14/morocco-creates-national-ai-hub-as-part-of-digital-morocco-2030-strategy/</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Implementation plan pending strategy launch</t>
+          <t>[Corrected 2026-09-17] Launch (2026-01-12) specifies implementation architecture: 3 priority themes, 2030 horizon, phased Jazari-institute network across 12 regions. Still enacted-partial, not comprehensive (2026-04-02 MWN piece calls it directional, not detailed).</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>AI-assisted (Cowork v2026-04-25)</t>
+          <t>AI sweep 2026-09-16 + author-approved correction</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Akwasi Appiah Obeng</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
@@ -14074,36 +14107,46 @@
         </is>
       </c>
       <c r="K144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>AI-assisted</t>
+          <t>Human-reviewed</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>https://regulations.ai/regulations/nigeria-summary</t>
+          <t>https://regulations.ai/regulations/nigeria-summary; https://aibase.ng/ai-ethics-policy/ai-regulations-in-nigeria/</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>NITDA Draft Code of Practice for AI 2025; NBA AI guidelines</t>
+          <t>[Corrected 2026-09-17] NITDA's AI Code of Practice (2025) remains an unfinalised draft as of mid-2026; issuing/oversight body not constituted. Downgraded from 2 (Enacted-Partial) to 1 (Nascent) — a draft is not an adopted standard.</t>
         </is>
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>AI-assisted (Cowork v2026-04-25)</t>
+          <t>AI sweep 2026-09-16 + author-approved correction</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>Akwasi Appiah Obeng</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
@@ -21814,31 +21857,46 @@
         </is>
       </c>
       <c r="K239" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>AI-assisted</t>
+          <t>Human-reviewed</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>https://primature.sn/publications/actualites/lancement-des-projets-structurants-du-new-deal-technologique-0</t>
         </is>
       </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>SENUM cloud and data infrastructure plans</t>
+          <t>[Corrected 2026-09-17] PM Sonko launched 7 structuring projects (2026-03-23-24) under New Deal Technologique: funded (~1,100bn FCFA, 2025-2034), sited (Diamniadio, Orana) sovereign cloud/data-centre commitment. Moves from nascent plan to enacted-partial.</t>
         </is>
       </c>
       <c r="Q239" t="inlineStr">
         <is>
-          <t>AI-assisted (Cowork v2026-04-25)</t>
+          <t>AI sweep 2026-09-16 + author-approved correction</t>
         </is>
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>Akwasi Appiah Obeng</t>
+        </is>
+      </c>
+      <c r="T239" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
@@ -38374,7 +38432,7 @@
         </is>
       </c>
       <c r="K446" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L446" t="inlineStr">
         <is>
@@ -38383,22 +38441,37 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>AI-assisted</t>
+          <t>Human-reviewed</t>
+        </is>
+      </c>
+      <c r="N446" t="inlineStr">
+        <is>
+          <t>https://www.dlapiperdataprotection.com/index.html?t=law&amp;c=CM</t>
         </is>
       </c>
       <c r="P446" t="inlineStr">
         <is>
-          <t>Law 2010/012 on cybersecurity has data elements; no comprehensive DPA law</t>
+          <t>[Corrected 2026-09-17] Law No. 2024/017 (23 Dec 2024) is a comprehensive data protection statute (cross-border regime, independent DPA). Old note ('Law 2010/012 cybersecurity elements only') missed this law entirely. Implementing decree not yet adopted, so 2 not 3.</t>
         </is>
       </c>
       <c r="Q446" t="inlineStr">
         <is>
-          <t>AI-assisted (Cowork v2026-04-25)</t>
+          <t>AI sweep 2026-09-16 + author-approved correction</t>
         </is>
       </c>
       <c r="R446" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="S446" t="inlineStr">
+        <is>
+          <t>Akwasi Appiah Obeng</t>
+        </is>
+      </c>
+      <c r="T446" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
@@ -38454,31 +38527,46 @@
         </is>
       </c>
       <c r="K447" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L447" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>AI-assisted</t>
+          <t>Human-reviewed</t>
+        </is>
+      </c>
+      <c r="N447" t="inlineStr">
+        <is>
+          <t>https://dataprotection.africa/cameroon/</t>
         </is>
       </c>
       <c r="P447" t="inlineStr">
         <is>
-          <t>No dedicated DPA</t>
+          <t>[Corrected 2026-09-17] Law No. 2024/017 creates a DPA in statute, but appointment/staffing unconfirmed as of March 2026 (dataprotection.africa: 'UNKNOWN IF APPOINTED'). Nascent (1), not absent (0) and not yet operational (2).</t>
         </is>
       </c>
       <c r="Q447" t="inlineStr">
         <is>
-          <t>AI-assisted (Cowork v2026-04-25)</t>
+          <t>AI sweep 2026-09-16 + author-approved correction</t>
         </is>
       </c>
       <c r="R447" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="S447" t="inlineStr">
+        <is>
+          <t>Akwasi Appiah Obeng</t>
+        </is>
+      </c>
+      <c r="T447" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
@@ -38614,31 +38702,51 @@
         </is>
       </c>
       <c r="K449" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L449" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>AI-assisted</t>
+          <t>Human-reviewed</t>
+        </is>
+      </c>
+      <c r="N449" t="inlineStr">
+        <is>
+          <t>https://www.dlapiperdataprotection.com/index.html?t=law&amp;c=CM</t>
         </is>
       </c>
       <c r="P449" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>[Corrected 2026-09-17] Law No. 2024/017 specifies DPA enforcement powers on paper (authorization, investigation, certification review); no implementing decree or documented enforcement yet. Conservative level per methodology section 7 (sources disagree on 1 vs 2 for enacted-but-undecreed statutes; see Review_flag).</t>
         </is>
       </c>
       <c r="Q449" t="inlineStr">
         <is>
-          <t>AI-assisted (Cowork v2026-04-25)</t>
+          <t>AI sweep 2026-09-16 + author-approved correction</t>
         </is>
       </c>
       <c r="R449" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="S449" t="inlineStr">
+        <is>
+          <t>Akwasi Appiah Obeng</t>
+        </is>
+      </c>
+      <c r="T449" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="U449" t="inlineStr">
+        <is>
+          <t>disputed</t>
         </is>
       </c>
     </row>
@@ -39974,31 +40082,46 @@
         </is>
       </c>
       <c r="K466" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L466" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>AI-assisted</t>
+          <t>Human-reviewed</t>
+        </is>
+      </c>
+      <c r="N466" t="inlineStr">
+        <is>
+          <t>https://www.dlapiperdataprotection.com/index.html?t=law&amp;c=CM</t>
         </is>
       </c>
       <c r="P466" t="inlineStr">
         <is>
-          <t>No comprehensive DPA law (Law 2010/012 has narrow data elements only)</t>
+          <t>[Corrected 2026-09-17] Law No. 2024/017 gives the new DPA statutory investigation/authorization powers, not yet operational. Old note asserted no comprehensive DPA law existed; superseded.</t>
         </is>
       </c>
       <c r="Q466" t="inlineStr">
         <is>
-          <t>Akwasi (Cecil-feedback revision, S1 rebalance)</t>
+          <t>AI sweep 2026-09-16 + author-approved correction</t>
         </is>
       </c>
       <c r="R466" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="S466" t="inlineStr">
+        <is>
+          <t>Akwasi Appiah Obeng</t>
+        </is>
+      </c>
+      <c r="T466" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
@@ -45094,7 +45217,7 @@
         </is>
       </c>
       <c r="K530" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L530" t="inlineStr">
         <is>
@@ -45103,22 +45226,37 @@
       </c>
       <c r="M530" t="inlineStr">
         <is>
-          <t>AI-assisted</t>
+          <t>Human-reviewed</t>
+        </is>
+      </c>
+      <c r="N530" t="inlineStr">
+        <is>
+          <t>https://techcentral.co.za/anc-piles-pressure-on-malatsi-over-ai-policy-fiasco/280761/</t>
         </is>
       </c>
       <c r="P530" t="inlineStr">
         <is>
-          <t>AI Government Discussion Document published 2024; National AI Policy Framework</t>
+          <t>[Corrected 2026-09-17] Draft National AI Policy (gazetted 2026-04-10) withdrawn ~2026-04-26/27 — 4 days before the 2026-04-30 cutoff — after fabricated academic citations were found. No policy re-adopted through Sept 2026. Downgraded from Enacted-Partial (2) to Nascent (1).</t>
         </is>
       </c>
       <c r="Q530" t="inlineStr">
         <is>
-          <t>AI-assisted (Cowork v2026-04-25)</t>
+          <t>AI sweep 2026-09-16 + author-approved correction</t>
         </is>
       </c>
       <c r="R530" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="S530" t="inlineStr">
+        <is>
+          <t>Akwasi Appiah Obeng</t>
+        </is>
+      </c>
+      <c r="T530" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
@@ -45174,7 +45312,7 @@
         </is>
       </c>
       <c r="K531" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L531" t="inlineStr">
         <is>
@@ -45183,22 +45321,37 @@
       </c>
       <c r="M531" t="inlineStr">
         <is>
-          <t>AI-assisted</t>
+          <t>Human-reviewed</t>
+        </is>
+      </c>
+      <c r="N531" t="inlineStr">
+        <is>
+          <t>https://techcentral.co.za/hallucination-hit-ai-policy-delayed-to-january-2027/281839/</t>
         </is>
       </c>
       <c r="P531" t="inlineStr">
         <is>
-          <t>Policy framework with strategic priorities</t>
+          <t>[Corrected 2026-09-17] Same withdrawal as F1.1 — the only document meeting the scope/specificity bar was pulled pre-cutoff. DCDT's post-withdrawal direction (confirmed 2026-07-29) is a lighter-touch framework with no adopted scope. Downgraded from 2 to 1.</t>
         </is>
       </c>
       <c r="Q531" t="inlineStr">
         <is>
-          <t>AI-assisted (Cowork v2026-04-25)</t>
+          <t>AI sweep 2026-09-16 + author-approved correction</t>
         </is>
       </c>
       <c r="R531" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="S531" t="inlineStr">
+        <is>
+          <t>Akwasi Appiah Obeng</t>
+        </is>
+      </c>
+      <c r="T531" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
@@ -69873,10 +70026,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2.08</v>
+        <v>2.1667</v>
       </c>
       <c r="F3" t="n">
-        <v>69.40000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="G3" t="n">
         <v>1.15</v>
@@ -69885,10 +70038,10 @@
         <v>38.3</v>
       </c>
       <c r="I3" t="n">
-        <v>31.1</v>
+        <v>33.9</v>
       </c>
       <c r="J3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -69901,14 +70054,14 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
@@ -69995,10 +70148,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2.33</v>
+        <v>2.2917</v>
       </c>
       <c r="F5" t="n">
-        <v>77.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="G5" t="n">
         <v>1.15</v>
@@ -70007,10 +70160,10 @@
         <v>38.3</v>
       </c>
       <c r="I5" t="n">
-        <v>39.5</v>
+        <v>38.1</v>
       </c>
       <c r="J5" t="n">
-        <v>27.9</v>
+        <v>26.9</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -70023,14 +70176,14 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
@@ -70117,10 +70270,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1.58</v>
+        <v>1.625</v>
       </c>
       <c r="F7" t="n">
-        <v>52.8</v>
+        <v>54.2</v>
       </c>
       <c r="G7" t="n">
         <v>0.4</v>
@@ -70129,10 +70282,10 @@
         <v>13.3</v>
       </c>
       <c r="I7" t="n">
-        <v>39.5</v>
+        <v>40.8</v>
       </c>
       <c r="J7" t="n">
-        <v>27.9</v>
+        <v>28.9</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -70145,14 +70298,14 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
@@ -70422,22 +70575,22 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.83</v>
+        <v>0.9583</v>
       </c>
       <c r="F12" t="n">
-        <v>27.8</v>
+        <v>31.9</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="H12" t="n">
-        <v>6.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>21.1</v>
+        <v>23.6</v>
       </c>
       <c r="J12" t="n">
-        <v>14.9</v>
+        <v>16.7</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -70450,14 +70603,14 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
@@ -70544,10 +70697,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2.62</v>
+        <v>2.5417</v>
       </c>
       <c r="F14" t="n">
-        <v>87.5</v>
+        <v>84.7</v>
       </c>
       <c r="G14" t="n">
         <v>2.1</v>
@@ -70556,10 +70709,10 @@
         <v>70</v>
       </c>
       <c r="I14" t="n">
-        <v>17.5</v>
+        <v>14.7</v>
       </c>
       <c r="J14" t="n">
-        <v>12.4</v>
+        <v>10.4</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -70575,11 +70728,11 @@
         <v>27</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
@@ -71499,17 +71652,17 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G13" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="H13" t="n">
         <v>4</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -72483,10 +72636,10 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="G37" t="n">
-        <v>83.3</v>
+        <v>75</v>
       </c>
       <c r="H37" t="n">
         <v>4</v>
@@ -73467,10 +73620,10 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="G61" t="n">
-        <v>50</v>
+        <v>58.3</v>
       </c>
       <c r="H61" t="n">
         <v>4</v>
@@ -75599,10 +75752,10 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="G113" t="n">
-        <v>8.300000000000001</v>
+        <v>33.3</v>
       </c>
       <c r="H113" t="n">
         <v>4</v>
@@ -75804,10 +75957,10 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="G118" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H118" t="n">
         <v>4</v>
@@ -76460,10 +76613,10 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="G134" t="n">
-        <v>58.3</v>
+        <v>41.7</v>
       </c>
       <c r="H134" t="n">
         <v>4</v>
@@ -79601,7 +79754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -81128,6 +81281,616 @@
       <c r="L28" t="inlineStr">
         <is>
           <t>Active monitoring and reports</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>v2.4</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>F1.1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>National AI strategy status</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>AI sweep 2026-09-16 + author-approved correction</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Baseline correction (missed pre-cutoff evidence)</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>'Maroc IA 2030' formally launched 2026-01-12, before the 2026-04-30 cutoff</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>https://www.moroccoworldnews.com/2026/01/274765/morocco-launches-maroc-ia-2030-roadmap-to-strengthen-ai-governance-digital-sovereignty/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>v2.4</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>MAR</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>F1.4</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Implementation plan with timelines</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>AI sweep 2026-09-16 + author-approved correction</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Baseline correction</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Launch specifies implementation architecture (3 themes, 2030 horizon, 12-region Jazari network)</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>https://techafricanews.com/2026/01/14/morocco-creates-national-ai-hub-as-part-of-digital-morocco-2030-strategy/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>v2.4</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NGA</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>F3.3</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Standards or technical guidance</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>AI sweep 2026-09-16 + author-approved correction</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Baseline correction (downgrade)</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>NITDA's AI Code of Practice remains an unfinalised draft, not an adopted standard</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>https://aibase.ng/ai-ethics-policy/ai-regulations-in-nigeria/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>v2.4</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>SEN</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>F5.2</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Cloud/data infrastructure policy</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>AI sweep 2026-09-16 + author-approved correction</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Baseline correction</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>PM launched 7 structuring projects 2026-03-23/24: funded, sited sovereign-cloud commitment</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>https://primature.sn/publications/actualites/lancement-des-projets-structurants-du-new-deal-technologique-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>v2.4</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Cameroon</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CMR</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>F2.1</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Data protection law status</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>AI sweep 2026-09-16 + author-approved correction</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Baseline correction</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Law No. 2024/017 (23 Dec 2024) is a comprehensive data protection statute, missed at original pass</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>https://www.dlapiperdataprotection.com/index.html?t=law&amp;c=CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>v2.4</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Cameroon</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>CMR</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>F2.2</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Data Protection Authority status</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>AI sweep 2026-09-16 + author-approved correction</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Baseline correction</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Same law creates a DPA in statute; appointment/staffing unconfirmed</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>https://dataprotection.africa/cameroon/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>v2.4</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Cameroon</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CMR</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>F2.4</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Enforcement framework in law</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>AI sweep 2026-09-16 + author-approved correction</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Baseline correction (disputed level, see Review_flag)</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Law specifies DPA enforcement powers on paper; no decree/enforcement yet. Verifiers split 1 vs 2; conservative value applied per methodology section 7.</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>https://www.dlapiperdataprotection.com/index.html?t=law&amp;c=CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>v2.4</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Cameroon</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>CMR</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>S1.1</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Statutory enforcement authority</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>AI sweep 2026-09-16 + author-approved correction</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Baseline correction</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Law No. 2024/017 gives the new DPA statutory investigation/authorization powers</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>https://www.dlapiperdataprotection.com/index.html?t=law&amp;c=CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>v2.4</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ZAF</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>F1.1</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>National AI strategy status</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>AI sweep 2026-09-16 + author-approved correction</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Baseline correction (downgrade)</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Draft National AI Policy withdrawn ~2026-04-26/27 (4 days pre-cutoff) after fabricated citations were found; not re-adopted through Sept 2026</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>https://techcentral.co.za/anc-piles-pressure-on-malatsi-over-ai-policy-fiasco/280761/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>v2.4</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ZAF</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>F1.2</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Strategy scope and specificity</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>2</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>AI sweep 2026-09-16 + author-approved correction</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Baseline correction (downgrade)</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Same withdrawal; no scope/specificity document in force at cutoff or since</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>https://techcentral.co.za/hallucination-hit-ai-policy-delayed-to-january-2027/281839/</t>
         </is>
       </c>
     </row>
